--- a/산출물/99_제출파일/서비스_기능정의서.xlsx
+++ b/산출물/99_제출파일/서비스_기능정의서.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4050" yWindow="2422" windowWidth="21600" windowHeight="11333" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,16 +13,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범위 정의" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -31,100 +30,141 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF191F28"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF6B7684"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF3182F6"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF191F28"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF191F28"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF3182F6"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF6B7684"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF191F28"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF191F28"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FFD12C2C"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF3182F6"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF6B7684"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF3182F6"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF191F28"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF1B7A3D"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FFB26A00"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF6B7684"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -176,25 +216,6 @@
       <bottom style="thin">
         <color rgb="FFD7DCE2"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD7DCE2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD7DCE2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD7DCE2"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -221,18 +242,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD7DCE2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD7DCE2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7DCE2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -242,8 +277,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -252,12 +285,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -278,15 +305,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -301,9 +319,36 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -667,429 +712,431 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24.5" customWidth="1" style="25" min="1" max="1"/>
+    <col width="30" customWidth="1" style="25" min="2" max="2"/>
+    <col width="22" customWidth="1" style="25" min="3" max="4"/>
+    <col width="14" customWidth="1" style="25" min="5" max="5"/>
+    <col width="12" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>서비스 기능 정의서</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>하모니(harmony) · 토스 안에서 악기를 연주하고 친구 트랙 위에 내 악기를 얹어 한 곡을 완성하는 미니앱</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="19.15" customHeight="1" s="25">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>1. 서비스 개요</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>서비스명</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>하모니 (harmony)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="22" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>한 줄 정의</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>악기를 연주해 트랙을 만들고, 친구 트랙 위에 내 연주를 얹어 한 곡을 완성하는 비동기 합주 미니앱</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="F6" s="22" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>App-in-Toss 미니앱 (토스 WebView, TDS 기반)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="22" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>대상 사용자</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>별도 가입 없이 토스 안에서 가볍게 연주·합주를 즐기려는 사용자</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="22" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>핵심 가치</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>가입 없는 즉시 진입 · 터치/제스처 연주 · 코드 한 줄로 친구와 합주 · 커뮤니티 합주(출처 얹기)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="22" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>제공 범위</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>출시 풀버전 — 익명 온보딩 / 악기 4종·코드·멜로디·드럼·제스처 연주 / 음색 / 녹음 / 로컬 저장 / 코드 공유·합주 / 커뮤니티 보드</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="22" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="38.25" customHeight="1" s="25">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>2. 문서 정보 · 변경 이력</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>작성자</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>변경 내용</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="22" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>v0.9</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>이상혁</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>초안 작성 — 기능 목록(FR) 골격 정의</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="22" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>이상혁</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>비기능(NFR)·정책(POL) 추가, MVP 범위 확정</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="52.5" customHeight="1" s="25">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>이상혁</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>기능 상세(액터·사전조건·처리·예외·우선순위) 보강, 데이터·범위표 신설</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="34.9" customHeight="1" s="25">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>이상혁</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>출시 풀버전 반영 — 악기·멜로디·드럼·음색·코드 직접선택·커뮤니티 기능 추가, 범위표 정정</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="22" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="38.25" customHeight="1" s="25">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>3. 기능 분류 체계 (ID 규칙)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>대분류</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>ID 접두어</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>포함 기능</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="22" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>온보딩·식별</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>익명 온보딩(토스 식별값 + 닉네임)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>PLAY</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>코드/멜로디/드럼 연주, 제스처 연주, 악기·음색 선택</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>녹음</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>메트로놈·카운트인, 이벤트 녹음·재생</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>저장</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>SAVE</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>로컬 저장·복구</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="22" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>공유·합주</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>SHARE</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>공유, 받기, 얹기, 동기화</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="22" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>합주 재생</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>JAM</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>합주 합쳐듣기</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="22" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>COMM</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>보드, 들어보기, 가져오기·합주 올리기, 댓글·신고</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>ID 형식: FR-{접두어}-{일련번호}. 우선순위는 MoSCoW(Must / Should / Could).</t>
         </is>
@@ -1131,1024 +1178,1025 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" style="25" min="1" max="1"/>
+    <col width="11" customWidth="1" style="25" min="2" max="2"/>
+    <col width="18" customWidth="1" style="25" min="3" max="3"/>
+    <col width="13" customWidth="1" style="25" min="4" max="4"/>
+    <col width="20" customWidth="1" style="25" min="5" max="5"/>
+    <col width="81" customWidth="1" style="25" min="6" max="6"/>
+    <col width="37.75" customWidth="1" style="25" min="7" max="7"/>
+    <col width="25.875" bestFit="1" customWidth="1" style="25" min="8" max="8"/>
+    <col width="10" customWidth="1" style="25" min="9" max="9"/>
+    <col width="14" customWidth="1" style="25" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>기능 요구사항 (FR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>각 기능의 액터·사전조건·처리 절차·예외·우선순위를 정의한다. (상태: 출시 풀버전 전 기능 구현 완료)</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>액터</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>사전조건</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>처리 절차</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>입출력 데이터</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>예외·폴백 처리</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>관련 화면</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="45" customHeight="1" s="25">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>FR-ID-01</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>온보딩</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>익명 온보딩</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>사용자, 시스템</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>미니앱 최초 진입</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>앱 진입 → 토스 getAnonymousKey로 기기 식별값 수신 → 닉네임 1회 입력 → 식별값·닉네임 로컬 저장 → 홈 진입</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>입력: 닉네임 / 출력: 익명 식별값, 홈</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>getAnonymousKey 미지원·실패 시 익명 폴백 식별값 발급 · 닉네임 미입력 시 진행 차단</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>온보딩, 홈</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="45" customHeight="1" s="25">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>FR-PLAY-01</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>코드 연주</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>연주 화면, 첫 터치로 오디오 활성</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>코드 패드(기본 4코드 C·Am·F·G) 탭 → 코드 사운드 재생. '코드 직접 고르기'로 28코드 중 최대 6개 선택해 패드 구성 가능</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>입력: 패드 터치/코드 선택 / 출력: 오디오 재생</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>오디오 미활성 시 첫 터치에서 활성화 처리</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>스튜디오, 코드 고르기 시트</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="25">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>FR-PLAY-02</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>제스처 연주</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>카메라 권한 허용, 연주 화면</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>카메라로 손 위치 인식 → 좌우 위치를 코드존에 매핑 → 편 손=지속 / 주먹=정지</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>입력: 카메라 프레임(손 위치) / 출력: 코드 재생·정지</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>권한 거부·인식 실패 시 터치 연주로 자동 폴백</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>스튜디오(제스처)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="25">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>FR-PLAY-03</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>멜로디 연주</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>멜로디 모드, 터치 입력</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>악기 선택(피아노 건반 / 기타·베이스 계이름 패드) → 키 탭 → 해당 음 재생. 옥타브 이동 가능</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>입력: 키 터치 / 출력: 음 재생</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>옥타브 한계 도달 시 해당 방향 버튼 비활성</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>스튜디오(멜로디)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="25">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR-PLAY-04</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>드럼 연주</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>드럼 악기 선택</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>드럼 패드 탭(킥·스네어·하이햇 등) → 드럼 사운드 재생(코드/멜로디 무관)</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>입력: 패드 터치 / 출력: 드럼 재생</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>스튜디오(드럼)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="25">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR-PLAY-05</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>악기·음색 선택</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>스튜디오 진입</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>악기 선택(피아노/기타/베이스/드럼) → 본문 레이아웃 전환 / 음색 선택(악기별 스타일 2종) → 소리만 변경</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>입력: 악기·음색 선택 / 출력: 레이아웃·음색 변경</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>녹음 중에는 변경 차단(트랙=한 악기)</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>스튜디오, 악기/음색 시트</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="25">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR-REC-01</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>녹음</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>메트로놈·카운트인</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>연주 화면에서 녹음 진입</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>박자(3/4·4/4·6/8 중 선택, 기본 4/4) · BPM(기본 100) 적용 → 녹음 시작 시 1마디 카운트인 → tick 클럭 구동</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>입력: 박자·BPM / 출력: 메트로놈 tick, 카운트인</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>탭 비활성 클럭 드리프트 시 타임스탬프 기준 보정</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>스튜디오, 메트로놈 시트</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="25">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR-REC-02</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>녹음</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>이벤트 녹음·재생</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>메트로놈 구동 중</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>tick 기준 이벤트(코드/음·시각) 기록 → 종료 시 트랙 데이터 생성 → 재생·정지, tick 동기 재현</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>입력: 연주 이벤트 / 출력: 트랙(이벤트 배열)</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>녹음 중 화면 이탈 시 현재까지 이벤트 보존</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>스튜디오(녹음·재생)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="25">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR-SAVE-01</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>저장</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>로컬 저장·복구</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>녹음된 트랙 존재</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>트랙을 로컬 저장 → 홈 '이어하기' 목록 노출 → 열기·삭제 → 재진입 시 복구</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>입력: 트랙·곡명 / 출력: 저장 목록</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>저장소 용량 초과 시 실패 안내 · 손상 항목 스킵</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>홈, 곡 저장 모달</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="25">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR-SHARE-01</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>공유·합주</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>공유</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>저장된 내 트랙 존재</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>내 트랙 업로드 → 서버가 공유 코드 발급 → 코드 클립보드 복사</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>입력: 트랙 / 출력: 공유 코드</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>업로드 실패 시 재시도 · 클립보드 미지원 시 코드 직접 노출</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>공유 세션</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="30" customHeight="1" s="25">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR-SHARE-02</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>공유·합주</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>받기</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>친구 공유 코드 보유</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>코드 입력/클립보드 → 서버에서 세션 트랙 로드</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>입력: 공유 코드 / 출력: 친구 트랙</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>코드 무효·네트워크 실패 시 프리로드(샘플)로 폴백</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>가져오기 시트</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="16" ht="30" customHeight="1" s="25">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR-SHARE-03</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>공유·합주</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>얹기</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>세션 로드됨</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>세션에 내 레이어(트랙) 추가 업로드 → 세션 트랙 목록 갱신(비동기 합주)</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>입력: 내 트랙 / 출력: 갱신된 세션</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>업로드 실패 시 로컬 보존 후 재시도</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>스튜디오, 가져오기</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="30" customHeight="1" s="25">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR-SHARE-04</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>공유·합주</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>동기화</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>세션 참여 중</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>1.5초 폴링으로 세션 신규 트랙 확인 → 변경 시 목록 반영(실시간 아님)</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>입력: 폴링 응답 / 출력: 세션 갱신</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>폴링 실패 시 다음 주기 재시도 · 중복 dedupe</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>스튜디오(합주)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="18" ht="30" customHeight="1" s="25">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR-JAM-01</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>합주 재생</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>합주 합쳐듣기</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>세션에 2개 이상 트랙</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>세션 전체 트랙을 트랙별 음색에 매핑 → tick 동기로 동시 재생</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>입력: 세션 트랙 / 출력: 합주 오디오</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>일부 트랙 로드 실패 시 가능한 트랙만 재생</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>스튜디오(합주)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="25">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>FR-COMM-01</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 보드</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 진입</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>공개 게시물 목록 로드(최신순/인기순) → 카드(제목·제작자·코드·재생수·파생수) 노출</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>입력: 정렬 / 출력: 게시물 목록</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>목록 없으면 빈 상태·시드 노출</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 보드</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="25">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>FR-COMM-02</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>들어보기</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>게시물 존재</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>게시물 카드 재생 → 트랙별 음색으로 미리듣기</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>입력: 카드 선택 / 출력: 미리듣기 재생</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>로드 실패 시 안내</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 보드</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="21" ht="45" customHeight="1" s="25">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>FR-COMM-03</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>가져오기·합주 올리기</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>게시물 존재 / 내 레이어</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>게시물 가져오기 → 스튜디오 로드(출처 코드 보존) → 내 레이어 얹어 '합주해서 올리기' → 새 게시물 발행(출처 표기·파생수 +1)</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>입력: 게시물·내 트랙 / 출력: 파생 게시물</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>빈 이름은 기본값 폴백 · 업로드 실패 시 재시도</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>커뮤니티, 올리기</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="30" customHeight="1" s="25">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>FR-COMM-04</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>댓글·신고·숨김</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>게시물 존재</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>게시물 댓글 작성 → 부적절 게시물·댓글 신고 → 신고 누적 시 자동 숨김(비가역)</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>입력: 댓글·신고 / 출력: 댓글 목록·숨김 처리</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>신고 중복·권한은 서버 검증</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 보드</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>비고: 전 기능 출시 풀버전 구현 완료. 실기기 9건 육안 검증(아이폰 13·갤럭시 S23 Ultra, IT-RT-02·03·04·05·06·08·10·11·12), 그 외 에뮬레이터·헤드리스 검증.</t>
         </is>
@@ -2171,411 +2219,413 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="25" min="1" max="1"/>
+    <col width="13" customWidth="1" style="25" min="2" max="2"/>
+    <col width="58" customWidth="1" style="25" min="3" max="3"/>
+    <col width="44" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="25">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>비기능 · 정책 요구사항</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>플랫폼 제약과 함께 성능·안정성·정책의 목표를 정의한다.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>비기능 요구사항 (NFR)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>목표·기준</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>NFR-01</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>HTTPS 필수(토스 WebView 요건) — nginx + Let's Encrypt</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>전 구간 TLS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>NFR-02</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>플랫폼/UX</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>핀치줌 비활성·자체 뒤로가기 UI 금지(토스 공통 가이드)</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>가이드 준수</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>NFR-03</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>비게임 카테고리 = TDS 사용(@toss/tds-mobile)</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>TDS 컴포넌트 우선</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>NFR-04</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>라이트 테마 고정</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>100% 라이트</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>품질</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>TypeScript strict 모드, reducer 단위테스트</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>strict / vitest 7파일 58케이스(58/58)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="25">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>NFR-06</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>성능·오디오</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>패드 터치 → 소리 재생까지 체감 즉시성(오디오 지연)</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>목표 수치 미정(정량 측정 미실시, 체감 기준 — 실기기 RT-02·08·11 육안)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>NFR-07</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>출시</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>앱인토스 앱 등록·심사 제출</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>2026-06-27 정식 전체공개(프로덕션) 출시 완료</t>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26 정식 전체공개(프로덕션) 출시 완료</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>NFR-08</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>성능·실시간성</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>동기화는 1.5초 폴링 방식(WebSocket 아님)</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>새 트랙 반영 ≤ 3초(폴링 1주기+로드)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>NFR-09</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>트랙은 코드+tick 이벤트 배열로 경량 저장</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>곡당 수 KB, 로컬 저장 한도(약 5MB) 내</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>NFR-10</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>호환</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>토스 WebView(iOS/Android) 표준 Web API만 사용</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>외부 네이티브 의존 없음</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>NFR-11</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>안정성</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>카메라·오디오·네트워크 실패 시 폴백 경로 보장</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>전 실패 케이스 폴백 정의</t>
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>정책 요구사항 (POL)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>근거</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>POL-01</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>식별</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>토스 식별만 허용·자체 로그인/회원가입 금지 → getAnonymousKey 사용</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>앱인토스 정책</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>POL-02</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>비게임(음악) 카테고리·표준 Web API(오디오·카메라)만 사용</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>앱인토스 정책</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>POL-03</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>공유</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>합주·커뮤니티는 코드/공개 게시 기반 — 불특정 사용자 추천·연결 없음</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>프라이버시/운영</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>POL-04</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>연령</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>성인·연령 확인 방식 — 현재 미구현(MVP 비범위), 정식 운영 확대 시 검토</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>POL Open Question(미정)</t>
         </is>
@@ -2593,250 +2643,251 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" style="25" min="1" max="1"/>
+    <col width="30" customWidth="1" style="25" min="2" max="2"/>
+    <col width="40" customWidth="1" style="25" min="3" max="3"/>
+    <col width="18" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>데이터 정의</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>공유·합주·커뮤니티의 기준이 되는 핵심 데이터 구조. (개념 수준)</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>핵심 엔티티</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>데이터</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>구성</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>저장 위치</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="30" customHeight="1" s="25">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>익명 식별값 (anonymousKey)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>토스 getAnonymousKey 반환값(또는 익명 폴백)</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>기기별 식별값. 가입·로그인 없이 사용자 구분</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>로컬 저장소</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>닉네임</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>사용자 입력 문자열(1회)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>트랙·게시물 표시용 이름. 인증 정보 아님</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>로컬 저장소</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>이벤트 (Event)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>tick, 코드/음, 동작(start/stop)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>연주 한 동작. tick 시각에 어떤 코드/음을 시작·정지</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>트랙 내부</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>트랙 (Track)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>트랙ID, 닉네임, 악기·음색, 이벤트 배열</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>한 사람의 한 번 연주 결과(이벤트 묶음)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>로컬 저장소 / 서버</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>세션 (Session)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>공유 코드, 트랙 배열, 출처 코드</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>합주 단위. 여러 트랙이 한 세션에 얹힘</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>서버</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="25">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>게시물 (커뮤니티)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>제목, 제작자, 코드, 출처 코드, 재생수·파생수</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 보드 공개 항목(세션 발행본)</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>서버</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>댓글·신고</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>게시물ID, 작성자, 내용 / 신고자, 누적수</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>커뮤니티 댓글 및 신고(누적 시 자동 숨김)</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>서버</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>공유 코드</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>세션 식별 코드(서버 발급)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>받기·얹기·동기화·가져오기의 키</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>서버</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>재생 기준</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>BPM 100, 4/4(기본), tick 클럭</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>트랙·세션 재생의 공통 타이밍 기준</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>앱 상수</t>
         </is>
@@ -2858,295 +2909,297 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" style="25" min="1" max="1"/>
+    <col width="46" customWidth="1" style="25" min="2" max="2"/>
+    <col width="14" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>범위 정의 (In / Out of Scope)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>출시 풀버전에 포함한 범위와, 의도적으로 제외(컷)한 범위 및 사유.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>포함 범위 (In Scope · 구현 완료)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="n"/>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="22" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>관련 ID</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>온보딩·식별</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>익명 온보딩 (토스 식별값 + 닉네임 1회)</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>FR-ID-01</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="25">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>연주</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>코드 연주(기본 4 + 직접 선택 28코드) · 멜로디(피아노/기타/베이스) · 드럼 · 제스처(폴백) · 악기·음색 선택</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>FR-PLAY-01~05</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>녹음</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>메트로놈(3/4·4/4·6/8)·카운트인 · 이벤트 녹음·재생</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>FR-REC-01~02</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>저장</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>로컬 저장·복구(홈 이어하기)</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>FR-SAVE-01</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>공유·합주</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>공유 / 받기 / 얹기 / 동기화(폴링)</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>FR-SHARE-01~04</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>합주 재생</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>세션 전체 트랙 합쳐듣기</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>FR-JAM-01</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>보드 · 들어보기 · 가져오기·합주 올리기 · 댓글·신고/숨김</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>FR-COMM-01~04</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>제외 범위 (Out of Scope · 컷)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="22" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>제외 항목</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>제외 사유</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>실시간 합주(WebSocket)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>폴링으로 대체 — 레이턴시·인프라 단순화</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>대체</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>계정·권한 체계</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>POL-01(자체 로그인 금지) — 익명 식별만</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>오디오 파일 업로드</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>이벤트 기반 경량 저장 채택(곡당 수 KB)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>대체</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>운영자 화면</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>MVP 불필요 — 신고 누적 자동 숨김으로 대체</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>후순위</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>사용자 추천·근처 사용자 연결</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>POL-03(불특정 추천·연결 금지)</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>성인·연령 확인</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>정식 출시 시 검토(POL-04)</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>후순위</t>
         </is>

--- a/산출물/99_제출파일/서비스_기능정의서.xlsx
+++ b/산출물/99_제출파일/서비스_기능정의서.xlsx
@@ -93,7 +93,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -101,23 +101,13 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="003182F6"/>
-        </stop>
-        <stop position="1">
-          <color rgb="0019C8B0"/>
-        </stop>
-      </gradientFill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3182F6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3182F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,7 +183,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">

--- a/산출물/99_제출파일/서비스_기능정의서.xlsx
+++ b/산출물/99_제출파일/서비스_기능정의서.xlsx
@@ -577,20 +577,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="3.5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -708,7 +708,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
     </row>
-    <row r="7" ht="111" customHeight="1">
+    <row r="7" ht="121" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>1</v>
       </c>
@@ -749,7 +749,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -765,11 +765,11 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>게임풍 인트로 아님. 화면 분기는 App.tsx 부트 플로우</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="111" customHeight="1">
+          <t>게임풍 인트로 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="121" customHeight="1">
       <c r="A8" s="8" t="n">
         <v>2</v>
       </c>
@@ -806,7 +806,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -822,11 +822,11 @@
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>가입·로그인 절차 없음. setNickname 시 trim 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="111" customHeight="1">
+          <t>가입·로그인 절차 없음. 닉네임 입력 시 앞뒤 공백 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="121" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>3</v>
       </c>
@@ -859,7 +859,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -875,11 +875,11 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>샌드박스 hash는 mock(per-user 식별 아님). 실사용자 식별은 정식배포·토스앱 QR 진입에서만 검증. 서버는 author_key 미검증, 레이트리밋은 IP 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="111" customHeight="1">
+          <t>샌드박스 hash는 mock(per-user 식별 아님). 실사용자 식별은 정식배포·토스앱 QR 진입에서만 검증. 서버는 작성자 키를 검증하지 않으며, 레이트리밋은 IP 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="121" customHeight="1">
       <c r="A10" s="8" t="n">
         <v>4</v>
       </c>
@@ -897,7 +897,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>SCR-04</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
@@ -928,11 +928,11 @@
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>선택 진입은 설정 화면. 커뮤니티 아바타는 본인 글에만 내 이모지 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="111" customHeight="1">
+          <t>프로필 선택 진입은 설정 화면. 커뮤니티 아바타는 본인 글에만 내 이모지 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="121" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>5</v>
       </c>
@@ -948,7 +948,11 @@
           <t>재진입 복구</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
           <t>앱·웹</t>
@@ -961,7 +965,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
@@ -981,7 +985,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="111" customHeight="1">
+    <row r="12" ht="121" customHeight="1">
       <c r="A12" s="8" t="n">
         <v>6</v>
       </c>
@@ -1003,7 +1007,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>SCR-04</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J12" s="13" t="inlineStr">
@@ -1041,7 +1045,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>▸ 연주-코드·제스처</t>
+          <t>▸ 연주</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -1055,7 +1059,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
     </row>
-    <row r="14" ht="141" customHeight="1">
+    <row r="14" ht="152" customHeight="1">
       <c r="A14" s="8" t="n">
         <v>7</v>
       </c>
@@ -1096,7 +1100,7 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr">
@@ -1114,17 +1118,17 @@
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>chordReducer는 한 번에 한 코드만 활성(mono). 같은 코드 재입력은 중복 noteOn 저장 안 함</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="141" customHeight="1">
+          <t>한 번에 한 코드만 활성(mono). 같은 코드 재입력은 중복 발음으로 저장하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="152" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>FN-PLAY-01</t>
+          <t>FN-PLAY-02</t>
         </is>
       </c>
       <c r="C15" s="15" t="n"/>
@@ -1151,7 +1155,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
@@ -1169,17 +1173,17 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>MAX_CHORDS=6. 코드 이름이 곧 tuning 키(예: G7·Am)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="156" customHeight="1">
+          <t>동시 선택 코드는 최대 6개</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="168" customHeight="1">
       <c r="A16" s="8" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>FN-PLAY-02</t>
+          <t>FN-PLAY-03</t>
         </is>
       </c>
       <c r="C16" s="15" t="n"/>
@@ -1210,7 +1214,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹·카메라</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
@@ -1229,20 +1233,20 @@
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>활성 판정 palm 모드=isOpen, 위치 기준점=중지 MCP(9). 양손 코드는 reducer 우회 직접 발음·녹음 중 이벤트 적재(recordRaw)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="111" customHeight="1">
+          <t>손바닥 모드는 손을 펼친 상태를 활성으로 판정하고, 위치 기준점은 중지 손가락 관절. 양손 코드는 녹음 중 이벤트로 함께 적재</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="121" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>FN-PLAY-02</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="n"/>
+          <t>FN-PLAY-04</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n"/>
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="10" t="inlineStr">
         <is>
@@ -1266,7 +1270,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>모바일(iOS·Android)·웹</t>
+          <t>모바일·웹·카메라</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
@@ -1282,72 +1286,51 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>실기기 검증 RT-04·05·06 아이폰 13·갤럭시 S23 Ultra 육안 성공(EV-203·204·205). 얼굴 검출(헤드뱅잉)은 베스트에포트, 실패해도 손 연주는 유지</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>▸ 연주-멜로디·드럼·악기</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="141" customHeight="1">
-      <c r="A19" s="8" t="n">
+          <t>실기기 검증 RT-04·05·06 아이폰 13·갤럭시 S23 Ultra 육안 성공(EV-203·204·205). 얼굴 검출(헤드뱅잉)은 베스트에포트로, 실패해도 손 연주는 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="152" customHeight="1">
+      <c r="A18" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>FN-PLAY-03</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>연주</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>FN-PLAY-05</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>멜로디 연주</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>피아노 건반(단음)</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>연주법을 멜로디로 바꾸고 악기가 피아노면 건반 표시(switchMode가 코드 잔류음 해제 후 전환)
 2옥타브 건반 표시(흰건반 도레미파솔라시 7음×2 = 14개, 검은건반 도#·레#·파#·솔#·라# 5개×2 = 10개), 건반 라벨은 한글 계이름
@@ -1360,49 +1343,49 @@
 - ensureAudio 대기 중 같은 포인터의 음이 바뀌면 : 늦게 도착한 발음 무시(포인터-음 일치 검사)</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>FR-PLAY-03. 출처 Studio.tsx renderPiano·melodyDown·melodyUp·shiftOctave·buildKeys(WHITE_PC·BLACK_PC·VISIBLE_OCTAVES 2·OCTAVE_MIN 1·OCTAVE_MAX 5), engine.ts downNote·upNote</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="141" customHeight="1">
-      <c r="A20" s="8" t="n">
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>표시 옥타브 2개, 옥타브 범위 1~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="152" customHeight="1">
+      <c r="A19" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>FN-PLAY-03</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>FN-PLAY-06</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>기타·베이스 계이름 패드</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-04</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>악기가 기타·베이스일 때 멜로디 모드에서 현×칸 패드 표시(NotePadGrid)
 행 = 개방현(기타 EADGBE 6현·베이스 EADG 4현), 높은 현이 위로(배열 역순 slice().reverse())
@@ -1415,49 +1398,49 @@
 - 전체화면 버튼(⛶) 탭 시 : 13칸으로 확장</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
-        <is>
-          <t>FR-PLAY-03. 출처 NotePadGrid.tsx, chords.ts STRINGS_GUITAR·STRINGS_BASS·FRETS_NORMAL 6·FRETS_FULL 13, lib/notes.ts transpose·solfa, Studio.tsx melodyDown·melodyUp</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="141" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>프렛은 기본 6칸·전체 13칸 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="152" customHeight="1">
+      <c r="A20" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>FN-PLAY-03</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>FN-PLAY-07</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>제스처 멜로디(카메라)</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹·카메라</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>입력 방식을 제스처로 바꾸면 멜로디는 손가락(finger) 모드 전용으로 고정(setGestureMode finger)
 손끝 위치를 건반(피아노)·현×칸(기타·베이스) 좌표로 환산, 셀 진입 상승엣지에서 발음
@@ -1470,53 +1453,53 @@
 - 카메라 전환(전·후면) 시 : 잠시 중단 후 재개(switchCamera, 실패 시 터치 폴백)</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>FR-PLAY-03·NFR-11. 출처 Studio.tsx loop(playMode melody 분기)·gMelodyOn·gMelodyOff·selectGesture·switchCamera, GestureMelodyPiano·GestureMelodyFretboard. 제스처 정확도는 코드 미확인(실기 측정 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="126" customHeight="1">
-      <c r="A22" s="8" t="n">
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>NFR-11. 제스처 정확도는 미확인(실기기 측정 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="136" customHeight="1">
+      <c r="A21" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>FN-PLAY-04</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>FN-PLAY-08</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>드럼 연주</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>드럼 패드 타격</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-05</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>악기를 드럼으로 선택하면 드럼 패드 표시(연주법 코드·멜로디 구분 없음)
 드럼 8피스 버튼 표시(크래시·하이햇·라이드·하이탐·미드탐·스네어·킥·플로어탐)
@@ -1528,53 +1511,53 @@
 - 제스처 입력 시 : 손 위치에서 가장 가까운 드럼 모양을 상승엣지로 타격(nearestDrumPiece, 가라지밴드풍 2D 배치)</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr">
-        <is>
-          <t>FR-PLAY-04. 출처 DrumPad.tsx(컴포넌트 주석은 '4분할'이나 실제 DRUM_PIECES 8개 버튼 렌더), chords.ts DRUM_PIECES·DRUM_KIT_LAYOUT·nearestDrumPiece, engine.ts triggerHit·playDrumSample·makeDrumKit, Studio.tsx hitDrum·loop(drum 분기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="126" customHeight="1">
-      <c r="A23" s="8" t="n">
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>드럼은 8개 패드로 렌더(컴포넌트 주석의 '4분할'과 다름)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="136" customHeight="1">
+      <c r="A22" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>FN-PLAY-05</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>FN-PLAY-09</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>악기·음색 선택</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>악기 고르기</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>설정 칩바의 악기 칩 탭 시 악기 선택 바텀시트 표시(피아노·기타·베이스·드럼 4종)
 악기 선택 시 setVoice로 소리 전환, 악기에 따라 본문 레이아웃 변경(건반·계이름 패드·드럼 패드)
@@ -1586,49 +1569,49 @@
 - 시트 바깥(backdrop) 탭 시 : 변경 없이 닫힘</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>FR-PLAY-05. 출처 InstrumentCombo.tsx pickInstrument, chords.ts INSTRUMENTS·STYLE_OPTIONS, Studio.tsx chooseVoice(phase 게이트 차단), engine.ts setVoice</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="156" customHeight="1">
-      <c r="A24" s="8" t="n">
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>악기 선택은 특정 단계에서 게이트로 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="168" customHeight="1">
+      <c r="A23" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>FN-PLAY-05</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>FN-PLAY-10</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>음색(스타일) 고르기</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>설정 칩바의 음색 칩 탭 시 음색 선택 바텀시트 표시(악기별 2종)
 악기별 음색: 피아노 1·2, 기타 1·2, 베이스 1·2, 드럼 1·2
@@ -1642,74 +1625,70 @@
 - 시트 바깥(backdrop) 탭 시 : 변경 없이 닫힘</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr">
-        <is>
-          <t>FR-PLAY-05. 출처 InstrumentCombo.tsx pickStyle(onPick=chooseVoice 수렴), chords.ts STYLE_OPTIONS, Studio.tsx chooseVoice, engine.ts setVoice·PRESETS·SAMPLE_DEFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>▸ 녹음·재생·편집</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="160" customHeight="1">
-      <c r="A26" s="8" t="n">
+      <c r="K23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>▸ 녹음</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="185" customHeight="1">
+      <c r="A25" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>FN-REC-01</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>스튜디오</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>녹음</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>녹음</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>메트로놈·카운트인</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>녹음 시작 시 메트로놈이 자동으로 켜짐(수동 on·off 없음)
 매 박(4분음표)마다 클릭음 출력, 마디 첫 박은 강박으로 구분
@@ -1725,49 +1704,49 @@
 녹음 종료 시 메트로놈 정지(메트로놈은 녹음 중에만 동작)</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>transport.ts startMetronome·onBeat, engine.ts playClick, Studio.tsx toggleRec·changeTimeSig·beatsForSig. 시각 표시는 Tone.Draw로 박 콜백 동기화</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="160" customHeight="1">
-      <c r="A27" s="8" t="n">
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>박 시각 표시는 박 콜백과 동기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="183" customHeight="1">
+      <c r="A26" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>FN-REC-01</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>FN-REC-02</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>이벤트 녹음·재생</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>연주 동작을 tick 단위 이벤트로 기록(벽시계 ms 사용 안 함)
 tick은 Transport 경과 초를 박 기준으로 환산(박당 4tick)
@@ -1782,49 +1761,45 @@
 - 녹음 정지 시 : 잡고 있던 미해제 노트를 패스 끝에서 해제(잔류음 방지)</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>events.ts NoteEvent·normalizeEvents·wireKey, transport.ts msToTick·tickToMs·transportSeconds, Studio.tsx recTick·scheduleEvents</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="126" customHeight="1">
-      <c r="A28" s="8" t="n">
+      <c r="K26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27" ht="136" customHeight="1">
+      <c r="A27" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>FN-REC-01</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>FN-REC-03</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>구간 반복(루프)</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>녹음 앞부분을 정한 마디 수만큼 잘라 정한 횟수로 이어붙임(예: 1마디 x 4 = 4마디)
 루프 단위 구간 [0, loopTicks)의 이벤트를 복제해 count회 타일링
@@ -1836,53 +1811,53 @@
 - 새로 녹음 시작 시 : 반복 상태 초기화(looped=false)</t>
         </is>
       </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>loop.ts loopEvents, Studio.tsx 반복 시트(loopBars·loopCount, barMs 산출)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="160" customHeight="1">
-      <c r="A29" s="8" t="n">
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>반복 구간은 마디 수·반복 횟수로 설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="185" customHeight="1">
+      <c r="A28" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>FN-REC-02</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>FN-REC-04</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>음 편집</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>피아노롤 편집</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-06</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>녹음된 take를 박자 그리드 위 블록(피아노롤)으로 표시
 on·off 이벤트를 노트로 페어링, 드럼은 포인트 블록으로 파싱
@@ -1899,49 +1874,49 @@
 - 취소 시 : 변경 폐기하고 편집 화면 닫기</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>NoteEditor.tsx, noteEdit.ts parseNotes·notesToEvents·quantizeNotes(순수·테스트). 음정값은 audio/tuning 단일 진실원</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="160" customHeight="1">
-      <c r="A30" s="8" t="n">
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>음정값은 단일 진실원(튜닝 정의)을 기준으로 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="183" customHeight="1">
+      <c r="A29" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>FN-REC-02</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>FN-REC-05</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>편집 화면 재생·스크럽</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-06</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>편집 화면에서 빨간 재생 위치선으로 현재 재생 지점 표시
 실행 시 현재 빨간 선 위치부터 재생(이미 지난 구간은 스킵)
@@ -1956,74 +1931,74 @@
 편집 화면 이탈·언마운트 시 재생 보이스·타이머 정리(잔류음·누수 방지)</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
-        <is>
-          <t>NoteEditor.tsx playFrom·play·restart·pause·스크럽(onHeadDown·Move·Up). 재생 보이스는 piano grand·drum analog 생성, performance.now 기반 rAF 진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>▸ 저장·공유·합주</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="111" customHeight="1">
-      <c r="A32" s="8" t="n">
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>편집 화면 재생 보이스는 피아노·드럼으로 생성, 진행 표시는 실시간 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>▸ 저장·공유</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="121" customHeight="1">
+      <c r="A31" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>FN-SAVE-01</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>저장·복구</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>저장·공유</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>로컬 저장</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>곡 저장</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>현재 take와 기존 레이어를 합쳐 멀티트랙 곡으로 localStorage('harmony.songs')에 저장
 저장 버튼 클릭 시 곡 이름 입력 모달 표시(자동값: 이어하기 곡이면 기존 이름, 아니면 '내 곡 N')
@@ -2034,53 +2009,53 @@
 - 빈 이름 입력 시 : 덮어쓰기는 기존 이름 유지, 신규는 '내 곡 N' 자동 명명</t>
         </is>
       </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>src/lib/storage.ts saveSong·newSongId, Studio.tsx openSave·doSave·buildLayered. BPM은 상수 BPM으로 저장</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="96" customHeight="1">
-      <c r="A33" s="8" t="n">
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>곡 저장 시 곡당 BPM 함께 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="105" customHeight="1">
+      <c r="A32" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>FN-SAVE-02</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>로컬 복구</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>곡 목록·열기·삭제</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>SCR-00</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>홈에서 저장 곡 목록 조회(listSongs), createdAt 내림차순 정렬로 최신 곡 먼저 노출
 곡 열기 시 멀티트랙은 전체 레이어로 적재하고 새 take는 비움(이어 녹음), 단일 take 구버전은 트랙 1개로 변환해 take에 적재
@@ -2090,57 +2065,53 @@
 - 멀티트랙 곡 열기 : 마지막 트랙 악기·스타일을 take 음색 기준으로 설정</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>storage.ts listSongs·deleteSong·songTracks. 구버전 events·instrument·style 단일 take 읽기 호환(신규 저장은 tracks 사용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="111" customHeight="1">
-      <c r="A34" s="8" t="n">
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>구버전 단일 take 곡 읽기 호환(신규 저장은 트랙 단위 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="121" customHeight="1">
+      <c r="A33" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>FN-SHARE-01</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>공유·합주</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>공유</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>코드 발급·복사</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>현재 take와 기존 레이어를 합쳐 세션으로 업로드(첫 트랙 POST /sessions, 나머지 순차 POST /sessions/:code/tracks)
 서버가 6자리 코드 발급(혼동문자 0·O·1·I 제외, crypto.randomInt 기반), 중복 시 재생성
@@ -2151,53 +2122,53 @@
 - 업로드 실패(네트워크) 시 : '공유 실패 네트워크 확인' 토스트</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
-        <is>
-          <t>share.ts createSession·addTrack·copyText, server.mjs genCode. 세션 이름 '하모니 합주' 고정</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="96" customHeight="1">
-      <c r="A35" s="8" t="n">
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>세션 기본 이름 '하모니 합주' 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="105" customHeight="1">
+      <c r="A34" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>FN-SHARE-02</t>
         </is>
       </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>받기</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>코드·클립보드 로드</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>받기 클릭 시 클립보드 텍스트에서 6자리 코드 정규식 추출 후 GET /sessions/:code로 친구 트랙 로드
 로드한 세션을 받기 확인 시트(pending)로 미리보기
@@ -2207,53 +2178,53 @@
 - 확인 완료 시 : 곡 신원 초기화(저장 시 새 곡), 'owner님 트랙 받았어요' 토스트</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>share.ts readClipboardCode·getSession·PRELOAD, Studio.tsx receive·confirmReceive. 숨김 세션은 서버 GET 404</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="111" customHeight="1">
-      <c r="A36" s="8" t="n">
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>숨김 세션은 서버 조회 시 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="121" customHeight="1">
+      <c r="A35" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>FN-SHARE-03</t>
         </is>
       </c>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>얹기</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>레이어 추가</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>현재 take를 한 트랙으로 쌓고 take를 비워 다음 악기 녹음을 준비(솔로·세션 공통)
 트랙에 닉네임·녹음 악기·스타일·생성시각 기록
@@ -2264,53 +2235,53 @@
 - 공개 세션에 소유자 아닌 키로 업로드 시 : 서버 403(소유자만 추가, 파생은 origin_code로)</t>
         </is>
       </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>Studio.tsx addLayer, share.ts addTrack, server.mjs MAX_TRACKS=16·published 소유자 검증. 네트워크 세션 트랙은 로컬 삭제 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="81" customHeight="1">
-      <c r="A37" s="8" t="n">
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>트랙은 세션당 최대 16개, 공개 세션은 소유자만 추가 가능. 네트워크 세션 트랙은 로컬 삭제 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>FN-SHARE-04</t>
         </is>
       </c>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>동기화</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>세션 폴링</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>세션 코드가 있는 동안 1.5초 간격으로 GET /sessions/:code 폴링해 트랙 목록 갱신(실시간 아님)
 응답 트랙으로 sessionTracks와 트랙 수 표시를 교체
@@ -2319,53 +2290,53 @@
 - 다른 참가자가 트랙 얹었을 때 : 다음 폴링에서 새 트랙 반영(반영 3초 이내 목표)</t>
         </is>
       </c>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>Studio.tsx 폴링 useEffect(SESSION_POLL_MS=1500), share.ts getSession. WebSocket 미사용(NFR-08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="111" customHeight="1">
-      <c r="A38" s="8" t="n">
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>동기화는 1.5초 간격 폴링. WebSocket 미사용(NFR-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="121" customHeight="1">
+      <c r="A37" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>FN-JAM-01</t>
         </is>
       </c>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>합쳐듣기</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>전체 합주 재생</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>모든 레이어와 현재 take를 합쳐 트랙별 녹음 악기·스타일로 동시 재생
 트랙마다 createVoice로 보이스 생성, 오디오 클럭 기준 scheduleEvents로 샘플정확 스케줄(레이어 싱크)
@@ -2376,53 +2347,53 @@
 - 라우트 이탈·언마운트 시 : 보이스 정리로 잔류음 방지</t>
         </is>
       </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>Studio.tsx playSession·stopJam·buildLayered·scheduleEvents. 실기기 RT-11 아이폰13·갤럭시 S23 Ultra 육안 성공(EV-208)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="111" customHeight="1">
-      <c r="A39" s="8" t="n">
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>실기기 RT-11 아이폰 13·갤럭시 S23 Ultra 육안 성공(EV-208)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="121" customHeight="1">
+      <c r="A38" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>FN-SHARE-05</t>
         </is>
       </c>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>커뮤니티 올리기</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>보드 공개·출처</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>SCR-ST-00</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>합친 곡을 커뮤니티 보드에 공개(POST /sessions, published=1), 닉네임·익명키·전체 레이어 수·멱등토큰 함께 전송
 가져온 곡(서버 code) 위에 쌓은 경우 그 code를 출처(origin_code)로 강제 기록해 원작자 표시
@@ -2433,74 +2404,74 @@
 - 업로드 실패 시 : '올리기 실패 네트워크 확인' 토스트</t>
         </is>
       </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>Studio.tsx openPublish·doPublish, share.ts publishSession, server.mjs content_hash·track_count dedup·origin 검증. FR-COMM-03 연계(파생수 +1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>보드 공개 시 콘텐츠 해시·트랙 수 기준 중복 제거, 출처 검증. 연계(파생수 +1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>▸ 커뮤니티</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="160" customHeight="1">
-      <c r="A41" s="8" t="n">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="185" customHeight="1">
+      <c r="A40" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>FN-COMM-01</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>커뮤니티</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>커뮤니티 보드</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>음원 목록·정렬·페이징</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>SCR-C01</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>커뮤니티 진입 시 listCommunity(30)로 보드 목록 1회 조회(공개·미숨김 세션만, events 제외 메타만)
 조회 시 x-anon-key 헤더로 익명키 전송, 항목별 내 좋아요 여부(liked) 포함
@@ -2517,53 +2488,53 @@
 - 조회 실패 시 : '불러오지 못했어요.' + '다시 시도' 버튼</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
-        <is>
-          <t>서버 GET /community, 커서(created_at·code) 지원. 서버 limit 기본 20·상한 50, 클라이언트는 30 전달. 정렬·페이징은 클라이언트 처리</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="160" customHeight="1">
-      <c r="A42" s="8" t="n">
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>커서(생성시각·코드) 기반 페이징. 서버 조회 한도 기본 20·상한 50, 클라이언트는 30 요청. 정렬·페이징은 클라이언트 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="185" customHeight="1">
+      <c r="A41" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>FN-COMM-02</t>
         </is>
       </c>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>들어보기</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>미리듣기·재생바 스크럽</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>SCR-C02</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>카드의 들어보기(▶) 탭 시 해당 음원을 미리듣기 재생
 트랙(events)은 보드 목록에 없으므로 getSession(code)로 지연 로드, 마운트 동안 캐시(재생 시 재요청 안 함)
@@ -2579,53 +2550,53 @@
 - 재생할 트랙 없음 : '재생할 내용이 없어요' 토스트</t>
         </is>
       </c>
-      <c r="K42" s="14" t="inlineStr">
-        <is>
-          <t>서버 GET /sessions/:code(매 GET play_count +1). setTimeout 스케줄+RAF 헤드 동일 벽시계로 드리프트 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="160" customHeight="1">
-      <c r="A43" s="8" t="n">
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>세션 조회 시마다 재생수 +1. 재생 스케줄과 진행 표시는 동일 기준 시계로 드리프트 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="185" customHeight="1">
+      <c r="A42" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>FN-COMM-03</t>
         </is>
       </c>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>가져오기·합주 올리기</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>담기(fork)·올리기(publish)·출처 보존</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>SCR-C03</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>카드의 담기(＋) 탭으로 음원 다중 선택, 재탭 시 선택 해제, 선택 시 하단 가져오기 바 노출
 가져오기 탭 시 선택한 각 code를 getSession으로 확보(병렬)해 스튜디오로 적재
@@ -2644,53 +2615,53 @@
 - 공유 실패 시 : '공유 실패, 네트워크 확인' 토스트</t>
         </is>
       </c>
-      <c r="K43" s="14" t="inlineStr">
-        <is>
-          <t>서버 POST /sessions(published, origin_code 실재 검증·INSERT only), POST /sessions/:code/tracks(공개 세션은 소유자만, 그 외 403). 멱등 토큰으로 연타 중복 차단</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="160" customHeight="1">
-      <c r="A44" s="8" t="n">
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>담기·올리기 시 출처 코드 실재 검증(신규 추가만 허용). 공개 세션 트랙 추가는 소유자만 가능하고 그 외 403. 멱등 토큰으로 연타 중복 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="185" customHeight="1">
+      <c r="A43" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>FN-COMM-04</t>
         </is>
       </c>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>반응·소통</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>댓글·신고·좋아요</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>SCR-C04</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>댓글(💬) 탭 시 패널 토글, 펼치면 getComments(code)로 댓글 목록 조회(미숨김만, 최신순)
 댓글 입력(placeholder '한마디 남기기', 최대 200자) 후 보내기 시 닉네임·익명키와 함께 addComment 전송, 성공 시 목록 갱신·첫 페이지 이동·카드 댓글 수 +1
@@ -2709,70 +2680,74 @@
 - 좋아요 실패 시 : 이전 상태로 되돌리고 '좋아요 실패' 토스트</t>
         </is>
       </c>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>서버 GET·POST /sessions/:code/comments, POST .../comments/:id/report(누적 3건 hidden), POST /sessions/:code/like(reactions UNIQUE). 신고자 식별=서버 IP, 자동숨김 복원(unhide) 미구현(비가역)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>▸ 설정·기타</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="81" customHeight="1">
-      <c r="A46" s="8" t="n">
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>신고 누적 3건이면 자동 숨김(좋아요는 사용자당 1회). 신고자 식별은 서버 IP 기준. 자동 숨김 복원은 미구현(비가역)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>▸ 설정</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>FN-SET-01</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>프로필 미리보기</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>이모지·닉네임 표시</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr"/>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>설정 진입 시 상단 카드에 이모지 프로필·닉네임·내 프로필 라벨 표시
 이모지는 localStorage harmony.emoji 저장값을 읽어 표시, 미저장 시 기본값 🎵
@@ -2781,49 +2756,53 @@
 - 아래 정보 카드 닉네임 행은 미저장 시 - 표시</t>
         </is>
       </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>프로필 카드와 정보 카드 닉네임 표기 폴백 문자열이 다름(게스트 / -)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="96" customHeight="1">
-      <c r="A47" s="8" t="n">
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>프로필 카드와 정보 카드의 닉네임 폴백 문자열이 다름('게스트' / '-')</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="105" customHeight="1">
+      <c r="A46" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>FN-SET-02</t>
         </is>
       </c>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>이모지 프로필</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>이모지 선택·변경</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr"/>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>이모지 프로필 행 탭 시 하단 바텀시트 열림
 선택지 24종 6열 그리드 표시(🎵 🎸 🎹 🥁 🎤 🎧 등)
@@ -2833,49 +2812,49 @@
 - 가입·로그인 절차 없음, 로컬 저장만 수행</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
-        <is>
-          <t>선택지·기본값 정의는 lib/identity.ts EMOJI_CHOICES</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="66" customHeight="1">
-      <c r="A48" s="8" t="n">
+      <c r="K46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47" ht="74" customHeight="1">
+      <c r="A47" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>FN-SET-03</t>
         </is>
       </c>
-      <c r="C48" s="15" t="n"/>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>프로필 정보</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>닉네임·버전 표시</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr"/>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>정보 카드에 닉네임·버전 행 표시
 버전은 코드 상수 1.0.0 고정 표기
@@ -2883,49 +2862,53 @@
 - 닉네임은 이 화면에서 변경 기능 없음(온보딩에서 입력)</t>
         </is>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="K47" s="14" t="inlineStr">
         <is>
           <t>버전 1.0.0은 하드코딩 값</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="96" customHeight="1">
-      <c r="A49" s="8" t="n">
+    <row r="48" ht="105" customHeight="1">
+      <c r="A48" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>FN-SET-04</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>개발자 모드</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr"/>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>개발자 모드 카드 탭 시 토글 on/off 전환
 부제 안내: FPS · 네트워크 · 손 스켈레톤 표시
@@ -2935,49 +2918,49 @@
 - localStorage 접근 실패 시 : 기본 false(off)</t>
         </is>
       </c>
-      <c r="K49" s="14" t="inlineStr">
-        <is>
-          <t>저장·조회 로직은 lib/settings.ts getDevMode·setDevMode</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="111" customHeight="1">
-      <c r="A50" s="8" t="n">
+      <c r="K48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49" ht="121" customHeight="1">
+      <c r="A49" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>FN-SET-05</t>
         </is>
       </c>
-      <c r="C50" s="15" t="n"/>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>2트랙 실증 패널</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>환경·식별키·TDS 표시</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr"/>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>개발자 모드 on일 때만 노출되는 실증 패널
 실행 환경 표시: web은 web (브라우저/AWS), 그 외 런타임 환경 문자열 표시
@@ -2988,49 +2971,53 @@
 TDS 렌더 행: 토스 환경이면 TdsBadge 동적 로드(로딩 중 로딩... 표시), 웹이면 미적용 (web) 표시</t>
         </is>
       </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>식별키 발급 분기·폴백은 lib/identity.ts getUserKey, TdsBadge는 isToss일 때만 lazy 로드</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="96" customHeight="1">
-      <c r="A51" s="8" t="n">
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>TDS 배지는 토스 환경일 때만 지연 로드</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="105" customHeight="1">
+      <c r="A50" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>FN-SET-06</t>
         </is>
       </c>
-      <c r="C51" s="15" t="n"/>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>법적 고지</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>이용약관·개인정보 처리방침</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr"/>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>법적 고지 섹션에 이용약관·개인정보 처리방침 행 표시
 각 행 탭 시 해당 문서를 스크롤 가능한 바텀시트 모달로 표시
@@ -3040,93 +3027,101 @@
 - 문서 본문 내용은 lib/legal.ts TERMS·PRIVACY 상수에서 로드</t>
         </is>
       </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>문서 원문 정의는 lib/legal.ts(코드 미확인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="8" t="n">
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>약관·개인정보 처리방침 문서 원문은 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="43" customHeight="1">
+      <c r="A51" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>FN-SET-07</t>
         </is>
       </c>
-      <c r="C52" s="15" t="n"/>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>내비게이션</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>홈 이동</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr"/>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="I52" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J52" s="13" t="inlineStr">
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>하단 홈으로 버튼 탭 시 go('home') 호출로 홈 라우트 이동
 - 별도 확인 절차 없이 즉시 이동</t>
         </is>
       </c>
-      <c r="K52" s="14" t="inlineStr"/>
-    </row>
-    <row r="53" ht="81" customHeight="1">
-      <c r="A53" s="8" t="n">
+      <c r="K51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>FN-SET-08</t>
         </is>
       </c>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>제스처 효과음</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>온오프 토글</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr"/>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>앱·웹</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>앱·웹</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
-        <is>
-          <t>모바일(iOS·Android)·웹</t>
-        </is>
-      </c>
-      <c r="J53" s="13" t="inlineStr">
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>모바일·웹·카메라</t>
+        </is>
+      </c>
+      <c r="J52" s="13" t="inlineStr">
         <is>
           <t>제스처 효과음(탬버린·박수·헤드뱅잉) on/off 상태를 localStorage harmony.fxon에 저장
 저장값이 0이 아니면 on으로 해석, 기본값 on
@@ -3135,39 +3130,36 @@
 - 비고: 토글 상태·읽기/쓰기 함수만 lib/settings.ts에 정의, Settings.tsx 화면에는 토글 UI 미배치</t>
         </is>
       </c>
-      <c r="K53" s="14" t="inlineStr">
-        <is>
-          <t>lib/settings.ts getFxOn·setFxOn 정의 존재, Settings.tsx에는 해당 토글 UI 없음(다른 화면에서 사용 추정)</t>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>효과음 온오프 저장·조회 로직은 있으나 설정 화면에 토글 UI 없음(다른 화면에서 사용 추정)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="C34:C39"/>
+  <mergeCells count="22">
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="D25:D27"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="D18:D20"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="C45:C52"/>
+    <mergeCell ref="C14:C23"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="C31:C38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C46:C53"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C26:C30"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="D8:D11"/>
     <mergeCell ref="C7:C12"/>
-    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="C25:C29"/>
     <mergeCell ref="A13:K13"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/산출물/99_제출파일/서비스_기능정의서.xlsx
+++ b/산출물/99_제출파일/서비스_기능정의서.xlsx
@@ -760,7 +760,7 @@
 - 정상 전환 시 : 닉네임 저장 여부 판정으로 진행
 - 저장 닉네임 있을 시 : 온보딩 건너뛰고 홈 진입
 - 저장 닉네임 없을 시 : 온보딩 화면 진입
-- 1300ms 전 화면 이탈 시 : 타이머 해제(중복 전환 방지)</t>
+- 1300ms 전 화면 이탈 시 : 전환 타이머 해제(중복 전환 방지)</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
@@ -814,7 +814,7 @@
           <t>닉네임 입력만으로 진입(가입·로그인 아님)
 닉네임 입력 필드 최대 16자, 공백만 입력 시 시작 불가
 시작하기 버튼은 닉네임 공백 또는 처리 중일 때 비활성
-시작하기 누르면 익명 식별키 발급·복원 후 닉네임을 localStorage(harmony.nickname)에 trim 저장
+시작하기 누르면 익명 식별키 발급·복원 후 닉네임을 앞뒤 공백 제거해 localStorage(harmony.nickname)에 저장
 - 진입 성공 시 : 홈 화면으로 이동
 - 식별키 발급 실패 시 : 시작하기 버튼 복구(잠시만요 표시 해제)
 - 닉네임 미입력 시 : 진행 차단(버튼 비활성)</t>
@@ -864,11 +864,11 @@
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>실행 환경에 따라 2트랙으로 익명 식별키 발급(getUserKey)
-토스 WebView·샌드박스 : getAnonymousKey 호출, 반환 type이 HASH면 toss_ 접두 + hash 사용
+          <t>실행 환경에 따라 2트랙으로 익명 식별키 발급
+토스 WebView·샌드박스 : 토스 익명키 발급을 호출, 반환 type이 HASH면 toss_ 접두 + hash 사용
 일반 브라우저(AWS)·미지원 환경 : crypto.getRandomValues 128bit 난수로 anon_ 접두 키 생성 후 localStorage(harmony.anonKey) 저장
-- getAnonymousKey 성공(HASH) 시 : toss_hash 키 반환
-- getAnonymousKey ERROR·undefined(토스앱 5.232.0 미만)·호출 throw 시 : anon_ 익명 폴백 키로 대체
+- 토스 익명키 발급 성공(HASH) 시 : toss_hash 키 반환
+- 토스 익명키 발급이 ERROR·undefined(토스앱 5.232.0 미만) 또는 호출에서 오류가 날 시 : anon_ 익명 폴백 키로 대체
 - 일반 브라우저 진입 시 : anon_ 폴백 키 사용
 - 폴백 키 기존 저장 시 : 저장 키 재사용</t>
         </is>
@@ -971,7 +971,7 @@
       <c r="J11" s="13" t="inlineStr">
         <is>
           <t>재진입 시 저장된 닉네임·식별키·이모지를 localStorage에서 복구
-앱 시작 시 getNickname으로 저장 닉네임 확인, 있으면 온보딩 건너뜀
+앱 시작 시 저장 닉네임을 확인, 있으면 온보딩 건너뜀
 식별키는 폴백 키일 경우 저장 키 재사용으로 동일 식별 유지(harmony.anonKey)
 이모지는 저장값 없으면 기본 🎵로 복구(harmony.emoji)
 - 저장 닉네임 있을 시 : 스플래시 후 바로 홈 진입
@@ -1105,13 +1105,13 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>코드 모드 진입 시 기본 팝 4코드(C·Am·F·G)를 패드로 노출(PRESET_POP)
+          <t>코드 모드 진입 시 기본 팝 4코드(C·Am·F·G)를 패드로 노출(기본 팝 프리셋)
 각 패드는 코드별 시그니처 색(C 파랑·Am 보라·F 초록·G 빨강)과 로마숫자(C:I·Am:vi·F:IV·G:V)를 함께 표시
-프리셋 외 추가로 고른 코드는 선택 순서대로 팔레트 색 순환(SIG)
+프리셋 외 추가로 고른 코드는 선택 순서대로 팔레트 색 순환
 패드를 누르면 해당 코드가 지속음으로 울리고, 떼면 멈춤
-첫 패드 터치 시 AudioContext unlock(ensureAudio) 후 발음
-- 발음 성공 시 : 패드 활성 표시(data-on), 다른 코드로 옮기면 이전 코드 자동 해제 후 새 코드 발음
-- 누르는 즉시 떼는 경우 : chordPointerRef에서 제거되어 발음 자체를 생략(지연-down 레이스 방지)
+첫 패드 터치 시 AudioContext를 깨운 뒤 발음
+- 발음 성공 시 : 패드 활성 표시, 다른 코드로 옮기면 이전 코드 자동 해제 후 새 코드 발음
+- 누르는 즉시 떼는 경우 : 보유 코드 목록에서 제거되어 발음 자체를 생략(지연-down 레이스 방지)
 - 포인터 이탈·취소(PointerCancel·PointerLeave) 시 : 보유 코드 해제
 - 선택된 코드가 0개면 : 패드 대신 '연주할 코드를 골라보세요' 안내</t>
         </is>
@@ -1227,7 +1227,7 @@
 전면(셀피) 카메라는 좌우 반전 적용, 후면 전환 가능
 현재 울리는 코드 존을 화면에서 하이라이트(코드 라벨 확대·해당 칸 현 진동)
 - 카메라 준비 중 : '카메라 준비 중...' 안내
-- 손이 화면을 빠르게 지나가는 중 : 신규 발음 보류(GESTURE_MOVE_GATE 초과 시 과다 트리거 억제)
+- 손이 화면을 빠르게 지나가는 중 : 신규 발음 보류(이동 속도 게이트 초과 시 과다 트리거 억제)
 - 1명(손 1개) 손 흔드는 중 : 그 손 연주 억제(효과음과 겹침 방지)</t>
         </is>
       </c>
@@ -1277,11 +1277,11 @@
         <is>
           <t>제스처와 터치 입력은 동시 바인딩 금지(둘 중 하나만 활성)
 제스처 진입 전 보유 중인 터치 코드를 먼저 해제(stuck 방지)
-터치 연주 중이거나 터치 종료 직후 200ms(GESTURE_RESUME_MS) 동안은 제스처 입력 무시
+터치 연주 중이거나 터치 종료 직후 200ms 동안은 제스처 입력 무시
 - 카메라 권한 거부·미지원·초기화 실패 시 : 제스처 루프 중단 후 터치 모드로 자동 복귀, '카메라를 쓸 수 없어 터치로 연주해요' 안내
 - 카메라 전환(전면·후면) 실패 시 : 동일하게 터치 폴백 + 동일 안내
-- 터치 모드로 전환 시 : 제스처 보유 코드·양손 잔류음 해제(releaseTwoHand), 전체화면 해제
-- 라우트 이탈·언마운트 시 : 카메라 정지·보유 코드 전체 해제(allOff)</t>
+- 터치 모드로 전환 시 : 제스처 보유 코드·양손 잔류음 해제, 전체화면 해제
+- 라우트 이탈·언마운트 시 : 카메라 정지·보유 코드 전체 해제</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
@@ -1332,15 +1332,15 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>연주법을 멜로디로 바꾸고 악기가 피아노면 건반 표시(switchMode가 코드 잔류음 해제 후 전환)
+          <t>연주법을 멜로디로 바꾸고 악기가 피아노면 건반 표시(모드 전환 시 코드 잔류음 해제 후 전환)
 2옥타브 건반 표시(흰건반 도레미파솔라시 7음×2 = 14개, 검은건반 도#·레#·파#·솔#·라# 5개×2 = 10개), 건반 라벨은 한글 계이름
-첫 터치 시 ensureAudio로 오디오 unlock 후 발음
-건반 누르면 해당 음 발음(downNote), 떼면 해제(upNote), 멀티터치 동시 누름 지원(poly)
+첫 터치 시 오디오를 깨워 unlock 후 발음
+건반 누르면 해당 음 발음, 떼면 해제, 멀티터치 동시 누름 지원(poly)
 옥타브 ▼/▲ 버튼으로 base 옥타브 1칸씩 이동(base 범위 1~5, 표시 음역 최저 C1, base 5에서 상단 B6), 라벨은 C{n} ~ B{n+1} 표시
-- 옥타브 이동 시 : 누르고 있던 음·셀 먼저 모두 해제 후 이동(clearMelody)
+- 옥타브 이동 시 : 누르고 있던 음·셀 먼저 모두 해제 후 이동
 - 옥타브 하한(1)·상한(5) 도달 시 : 해당 버튼 흐리게(opacity 0.4)·비활성(disabled)
 - 전체화면 버튼(⛶) 탭 시 : 큰 건반(높이 확대)으로 전환, CSS 회전은 안 함, '폰을 가로로 돌리면 넓게 써요' 안내 표시
-- ensureAudio 대기 중 같은 포인터의 음이 바뀌면 : 늦게 도착한 발음 무시(포인터-음 일치 검사)</t>
+- 오디오 unlock 대기 중 같은 포인터의 음이 바뀌면 : 늦게 도착한 발음 무시(포인터-음 일치 검사)</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>악기가 기타·베이스일 때 멜로디 모드에서 현×칸 패드 표시(NotePadGrid)
-행 = 개방현(기타 EADGBE 6현·베이스 EADG 4현), 높은 현이 위로(배열 역순 slice().reverse())
+          <t>악기가 기타·베이스일 때 멜로디 모드에서 현×칸 패드 표시
+행 = 개방현(기타 EADGBE 6현·베이스 EADG 4현), 높은 현이 위로(배열 역순으로 뒤집어 표시)
 열 = 0칸(개방현)부터 한 칸 = 반음(크로매틱: 도 도# 레 레#...), 칸 수 일반 6칸·전체화면 13칸
-각 칸 라벨은 계이름(solfa), 개방현 라벨은 음명+옥타브 숫자
-칸을 누르면 개방현 기준 반음 누적 음 발음(transpose로 음명 산출 후 downNote)
-- 누른 칸 : 파란색 강조(held 표시, var(--blue))
+각 칸 라벨은 계이름, 개방현 라벨은 음명+옥타브 숫자
+칸을 누르면 개방현 기준 반음 누적 음 발음(누적 반음으로 음명 산출 후 발음)
+- 누른 칸 : 파란색 강조(눌림 표시, var(--blue))
 - 떼면 : 해제, 멀티터치 동시 발음 지원(poly)
 - 가로로 길면 : 좌우 스크롤(touchAction pan-x), 개방현 라벨 열은 좌측 고정(sticky)
 - 전체화면 버튼(⛶) 탭 시 : 13칸으로 확장</t>
@@ -1442,15 +1442,15 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>입력 방식을 제스처로 바꾸면 멜로디는 손가락(finger) 모드 전용으로 고정(setGestureMode finger)
+          <t>입력 방식을 제스처로 바꾸면 멜로디는 손가락(finger) 모드 전용으로 고정
 손끝 위치를 건반(피아노)·현×칸(기타·베이스) 좌표로 환산, 셀 진입 상승엣지에서 발음
 한 현을 가로로 쓸면 연속 셀 전이로 글리산도 효과, 양손 각각 한 음씩 동시 발음(최대 2손)
-눌린 음·셀은 오버레이로 하이라이트(updateMelodyActive)
-- 손이 빠르게 지나갈 때(속도 게이트 GESTURE_MOVE_GATE 초과) : 새 발음 보류(과다 트리거 억제)
-- 셀 밖으로 나가면 : 직전 음 해제(gMelodyOff)
+눌린 음·셀은 오버레이로 하이라이트
+- 손이 빠르게 지나갈 때(이동 속도 게이트 초과) : 새 발음 보류(과다 트리거 억제)
+- 셀 밖으로 나가면 : 직전 음 해제
 - 손바닥 모드(비포인팅)일 때 : 발음 안 함
-- 카메라 사용 불가 시 : 터치로 폴백(selectTouch), '카메라를 쓸 수 없어 터치로 연주해요' 안내(연주 중단 없음)
-- 카메라 전환(전·후면) 시 : 잠시 중단 후 재개(switchCamera, 실패 시 터치 폴백)</t>
+- 카메라 사용 불가 시 : 터치로 폴백, '카메라를 쓸 수 없어 터치로 연주해요' 안내(연주 중단 없음)
+- 카메라 전환(전·후면) 시 : 잠시 중단 후 재개(실패 시 터치 폴백)</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
@@ -1503,12 +1503,12 @@
         <is>
           <t>악기를 드럼으로 선택하면 드럼 패드 표시(연주법 코드·멜로디 구분 없음)
 드럼 8피스 버튼 표시(크래시·하이햇·라이드·하이탐·미드탐·스네어·킥·플로어탐)
-패드를 누르면 즉시 1회 타격음 재생(원샷, onPointerDown 1회)
+패드를 누르면 즉시 1회 타격음 재생(원샷, 누르는 순간 1회)
 실제 드럼 샘플 로드 시 샘플 재생, 미로드·실패 시 합성 드럼킷으로 폴백(항상 소리남)
-- 타격 시 : 해당 패드·색 약 140ms 깜빡임(flashPiece, 어디를 쳤는지 표시)
-- 녹음 중 타격 시 : 'hit' 이벤트로 기록(chordReducer hit)
+- 타격 시 : 해당 패드·색 약 140ms 깜빡임(어디를 쳤는지 표시)
+- 녹음 중 타격 시 : 'hit' 이벤트로 기록
 - 전체화면 버튼(⛶) 탭 시 : 큰 패드로 전환
-- 제스처 입력 시 : 손 위치에서 가장 가까운 드럼 모양을 상승엣지로 타격(nearestDrumPiece, 가라지밴드풍 2D 배치)</t>
+- 제스처 입력 시 : 손 위치에서 가장 가까운 드럼 모양을 상승엣지로 타격(가라지밴드풍 2D 배치)</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
@@ -1560,12 +1560,12 @@
       <c r="J22" s="13" t="inlineStr">
         <is>
           <t>설정 칩바의 악기 칩 탭 시 악기 선택 바텀시트 표시(피아노·기타·베이스·드럼 4종)
-악기 선택 시 setVoice로 소리 전환, 악기에 따라 본문 레이아웃 변경(건반·계이름 패드·드럼 패드)
-악기 바꾸면 해당 악기의 첫 음색으로 자동 리셋(STYLE_OPTIONS 첫 값), 기존 코드·멜로디 잔류음 해제(allOff·clearMelody)
-- 악기 선택 직후 : 미리듣기 1회 재생(드럼=킥 triggerHit, 그 외=C 코드 약 0.5초 후 chordOff)
-- 드럼 외 악기 선택 시 : 입력 방식을 터치로 되돌림(selectTouch)
-- 녹음 중(카운트인·녹음, phase!=='idle') 변경 시도 시 : 변경 차단, '녹음 중에는 악기를 바꿀 수 없어요' 토스트 표시
-- 현재 선택 악기 : 체크(✓)와 강조(data-on) 표시
+악기 선택 시 소리를 전환하고, 악기에 따라 본문 레이아웃 변경(건반·계이름 패드·드럼 패드)
+악기 바꾸면 해당 악기의 첫 음색으로 자동 리셋(스타일 목록 첫 값), 기존 코드·멜로디 잔류음 해제
+- 악기 선택 직후 : 미리듣기 1회 재생(드럼=킥 1회 타격, 그 외=C 코드 약 0.5초 후 해제)
+- 드럼 외 악기 선택 시 : 입력 방식을 터치로 되돌림
+- 녹음 중(카운트인·녹음, 대기 상태가 아닐 때) 변경 시도 시 : 변경 차단, '녹음 중에는 악기를 바꿀 수 없어요' 토스트 표시
+- 현재 선택 악기 : 체크(✓)와 강조 표시
 - 시트 바깥(backdrop) 탭 시 : 변경 없이 닫힘</t>
         </is>
       </c>
@@ -1615,12 +1615,12 @@
         <is>
           <t>설정 칩바의 음색 칩 탭 시 음색 선택 바텀시트 표시(악기별 2종)
 악기별 음색: 피아노 1·2, 기타 1·2, 베이스 1·2, 드럼 1·2
-음색 선택도 악기 선택과 동일 경로(chooseVoice)로 수렴, 화면·레이아웃은 그대로 두고 소리(오실레이터·엔벨로프·샘플)만 변경(setVoice)
+음색 선택도 악기 선택과 동일 경로로 수렴, 화면·레이아웃은 그대로 두고 소리(오실레이터·엔벨로프·샘플)만 변경
 샘플 음원 로드 시 실제 악기 샘플, 미로드 시 합성 프리셋으로 폴백
-- 음색 변경 시 : 잡고 있던 음·코드 해제(allOff·clearMelody, setVoice 내부 releaseAll) 후 새 음색 적용
+- 음색 변경 시 : 잡고 있던 음·코드 해제(소리 전환 시 내부에서 모든 음 해제) 후 새 음색 적용
 - 음색 변경 직후 : 미리듣기 1회 재생(드럼=킥, 그 외 C 코드 약 0.5초)
-- 드럼 외 음색 선택 시 : 입력 방식이 터치로 복귀(selectTouch)
-- 녹음 중(phase!=='idle') 변경 시도 시 : 차단·토스트(악기 칩과 동일 차단)
+- 드럼 외 음색 선택 시 : 입력 방식이 터치로 복귀
+- 녹음 중(대기 상태가 아닐 때) 변경 시도 시 : 차단·토스트(악기 칩과 동일 차단)
 - 현재 선택 음색 : 체크(✓) 표시
 - 시트 바깥(backdrop) 탭 시 : 변경 없이 닫힘</t>
         </is>
@@ -1697,8 +1697,8 @@
 박자는 메트로놈 시트에서 3/4·4/4·6/8 중 선택(마디당 박 수 3·4·6, 기본 4/4)
 템포(BPM)는 ±1 버튼으로 조절(기본 100, 범위 40~240)
 진행 중 템포·박자 변경 시 즉시 반영
-녹음 버튼을 누르면 카운트인 단계로 진입(phase=countin)
-1마디 카운트인 후 자동으로 녹음 단계로 전환(bar가 1에 도달하면 recording)
+녹음 버튼을 누르면 카운트인 단계로 진입
+1마디 카운트인 후 자동으로 녹음 단계로 전환(마디가 1에 도달하면 녹음 시작)
 카운트인 동안 화면 상단에 남은 박 수 표시(카운트인 N)
 카운트인 중 누르고 있던 코드·음은 녹음 시작 시점에 이어서 적재
 녹음 종료 시 메트로놈 정지(메트로놈은 녹음 중에만 동작)</t>
@@ -1750,13 +1750,13 @@
         <is>
           <t>연주 동작을 tick 단위 이벤트로 기록(벽시계 ms 사용 안 함)
 tick은 Transport 경과 초를 박 기준으로 환산(박당 4tick)
-녹음 시작 시점(recordStartRef)을 0틱 기준으로 잡아 경과 틱 산출
+녹음 시작 시점을 0틱 기준으로 잡아 경과 틱 산출
 이벤트는 코드(chord)·멜로디(melody)·드럼(drum) 세 종류의 노트 이벤트로 구분
 코드·멜로디는 on·off 한 쌍, 드럼은 off 없는 원샷(hit)으로 기록
-드럼은 와이어 저장 시 'drum:피스' 형태로 직렬화(백엔드 스키마 무변경)
-저장·공유된 이벤트는 normalizeEvents로 복원(kind 없는 과거 데이터·교차 사용자 트랙 호환)
+드럼은 전송 저장 시 'drum:피스' 형태로 직렬화(백엔드 스키마 무변경)
+저장·공유된 이벤트는 표준 형식으로 복원(kind 없는 과거 데이터·교차 사용자 트랙 호환)
 재생 시 녹음한 악기 보이스로 각 이벤트를 tick→ms 환산해 스케줄
-오디오 클럭 기준으로 스케줄해 레이어 간 싱크 유지(setTimeout 지터 제거)
+오디오 클럭 기준으로 스케줄해 레이어 간 싱크 유지(타이머 지터 제거)
 - 녹음 중 악기 변경 시도 시 : '녹음 중에는 악기를 바꿀 수 없어요' 안내
 - 녹음 정지 시 : 잡고 있던 미해제 노트를 패스 끝에서 해제(잔류음 방지)</t>
         </is>
@@ -1802,13 +1802,13 @@
       <c r="J27" s="13" t="inlineStr">
         <is>
           <t>녹음 앞부분을 정한 마디 수만큼 잘라 정한 횟수로 이어붙임(예: 1마디 x 4 = 4마디)
-루프 단위 구간 [0, loopTicks)의 이벤트를 복제해 count회 타일링
+루프 단위 구간 [0, 루프 길이)의 이벤트를 복제해 정한 횟수만큼 타일링
 루프 길이는 마디 그리드(마디당 박 수 x 4tick)에 정렬해 메트로놈과 드리프트 방지
-경계를 넘어 열린 비드럼 노트(코드·멜로디)는 루프 끝(loopTicks-1)에서 off로 닫아 음 끌림 방지
+경계를 넘어 열린 비드럼 노트(코드·멜로디)는 루프 끝(루프 길이-1)에서 off로 닫아 음 끌림 방지
 드럼은 off 없는 원샷이라 닫지 않음
 이벤트 복제 방식이라 저장·공유·재생 결과가 동일하게 일관
-- loopTicks 또는 count가 0 이하인 경우 : 원본 이벤트를 그대로 복제 반환
-- 새로 녹음 시작 시 : 반복 상태 초기화(looped=false)</t>
+- 루프 길이 또는 반복 횟수가 0 이하인 경우 : 원본 이벤트를 그대로 복제 반환
+- 새로 녹음 시작 시 : 반복 상태 초기화(반복 해제)</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
@@ -1859,18 +1859,18 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>녹음된 take를 박자 그리드 위 블록(피아노롤)으로 표시
+          <t>녹음된 테이크를 박자 그리드 위 블록(피아노롤)으로 표시
 on·off 이벤트를 노트로 페어링, 드럼은 포인트 블록으로 파싱
-멜로디만 있는 take는 연속 반음 피아노롤(세로 드래그로 음정), 그 외는 값별 이산 레인
+멜로디만 있는 테이크는 연속 반음 피아노롤(세로 드래그로 음정), 그 외는 값별 이산 레인
 블록을 가로로 끌어 시간 위치 이동(1tick 단위)
-멜로디 전용 피아노롤에서 블록을 세로로 끌어 음정 변경(lo~hi 범위 제한)
+멜로디 전용 피아노롤에서 블록을 세로로 끌어 음정 변경(최저~최고 범위 제한)
 블록 오른쪽 끝(18px 이내)을 끌어 길이 조절(최소 1tick), 드럼은 길이 조절 없음
 선택 노트를 버튼으로 미세 이동(◀·▶, 1/8박 단위)
 선택한 멜로디 노트를 버튼으로 반음 조옮김(▲음·▼음)
 선택 노트 또는 전체를 1/8박 그리드에 퀀타이즈(맞춤·전체 맞춤)
 선택 노트 삭제
 - 편집할 노트가 없는 경우 : '편집할 노트가 없어요. 먼저 녹음해 주세요.' 안내
-- 적용 시 : 편집 결과를 이벤트로 직렬화해 take에 반영(동일 tick은 off 먼저 정렬)
+- 적용 시 : 편집 결과를 이벤트로 직렬화해 테이크에 반영(동일 tick은 off 먼저 정렬)
 - 취소 시 : 변경 폐기하고 편집 화면 닫기</t>
         </is>
       </c>
@@ -1923,12 +1923,12 @@
 끝까지 재생된 상태에서 실행 시 처음부터 재생
 다시듣기 시 위치를 처음으로 되돌리고 즉시 재생
 정지 시 오디오만 멈추고 빨간 선은 현재 위치에 유지(처음으로 안 돌아감)
-재생 중 플레이헤드가 지나는 블록은 강조 표시(밝기·확대·글로우)
+재생 중 위치선이 지나는 블록은 강조 표시(밝기·확대·글로우)
 빨간 선을 끌어 재생 위치 스크럽(전체 높이 그랩)
 - 재생 중 빨간 선 드래그 시 : 재생을 멈추고 위치만 이동
 - 재생이 끝에 도달한 경우 : 끝 위치에서 멈춤(자동 복귀 안 함)
-재생 진행에 따라 가로 스크롤 자동 추적(플레이헤드가 화면 끝에 가까우면 스크롤)
-편집 화면 이탈·언마운트 시 재생 보이스·타이머 정리(잔류음·누수 방지)</t>
+재생 진행에 따라 가로 스크롤 자동 추적(위치선이 화면 끝에 가까우면 스크롤)
+편집 화면 이탈·종료 시 재생 보이스·타이머 정리(잔류음·누수 방지)</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
@@ -2002,10 +2002,10 @@
         <is>
           <t>현재 take와 기존 레이어를 합쳐 멀티트랙 곡으로 localStorage('harmony.songs')에 저장
 저장 버튼 클릭 시 곡 이름 입력 모달 표시(자동값: 이어하기 곡이면 기존 이름, 아니면 '내 곡 N')
-같은 id 곡은 목록에서 제거 후 새로 push(덮어쓰기), createdAt 갱신
+같은 id 곡은 목록에서 제거 후 새로 추가(덮어쓰기), 생성시각 갱신
 - 저장할 연주가 없을 때 : '저장할 연주가 없어요' 토스트 출력, 모달 미표시
 - 이어하기 곡 덮어쓰기 : 같은 id·이름으로 갱신, '이름 저장됨 (트랙 N)' 토스트
-- 새 곡으로 저장 : newSongId로 새 id 발급 후 별도 곡 저장
+- 새 곡으로 저장 : 새 곡 id를 발급한 뒤 별도 곡으로 저장
 - 빈 이름 입력 시 : 덮어쓰기는 기존 이름 유지, 신규는 '내 곡 N' 자동 명명</t>
         </is>
       </c>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>홈에서 저장 곡 목록 조회(listSongs), createdAt 내림차순 정렬로 최신 곡 먼저 노출
+          <t>홈에서 저장 곡 목록을 조회하고, 생성시각 내림차순 정렬로 최신 곡 먼저 노출
 곡 열기 시 멀티트랙은 전체 레이어로 적재하고 새 take는 비움(이어 녹음), 단일 take 구버전은 트랙 1개로 변환해 take에 적재
 삭제는 해당 id를 목록에서 제외해 localStorage에 재기록
 - 저장 데이터 없을 때 : 빈 목록 반환
@@ -2115,7 +2115,7 @@
         <is>
           <t>현재 take와 기존 레이어를 합쳐 세션으로 업로드(첫 트랙 POST /sessions, 나머지 순차 POST /sessions/:code/tracks)
 서버가 6자리 코드 발급(혼동문자 0·O·1·I 제외, crypto.randomInt 기반), 중복 시 재생성
-발급 코드를 navigator.clipboard로 클립보드 복사
+발급 코드를 클립보드에 복사
 - 공유할 연주 없을 때 : 동작 중단
 - 복사 성공 시 : '공유 코드 복사됨 · CODE' 토스트
 - 복사 실패(클립보드 미허용) 시 : '공유 코드 · CODE' 토스트로 코드만 노출
@@ -2170,9 +2170,9 @@
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>받기 클릭 시 클립보드 텍스트에서 6자리 코드 정규식 추출 후 GET /sessions/:code로 친구 트랙 로드
+          <t>받기 클릭 시 클립보드 텍스트에서 6자리 코드를 정규식으로 추출한 뒤 GET /sessions/:code로 친구 트랙 로드
 로드한 세션을 받기 확인 시트(pending)로 미리보기
-확인 시 받은 트랙을 레이어(sessionTracks)로만 적재하고 take는 비움(내 악기로 새로 녹음해 얹기), sessionCode 설정
+확인 시 받은 트랙을 레이어로만 적재하고 take는 비움(내 악기로 새로 녹음해 얹기), 세션 코드 설정
 - 클립보드에 코드 없거나 읽기 실패 시 : 프리로드 데모(DEMO01 토스밴드 C·G·Am·F)로 폴백
 - 받을 트랙이 없을 때 : '받을 트랙이 없어요' 토스트
 - 확인 완료 시 : 곡 신원 초기화(저장 시 새 곡), 'owner님 트랙 받았어요' 토스트</t>
@@ -2283,11 +2283,11 @@
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>세션 코드가 있는 동안 1.5초 간격으로 GET /sessions/:code 폴링해 트랙 목록 갱신(실시간 아님)
-응답 트랙으로 sessionTracks와 트랙 수 표시를 교체
-진입 즉시 1회 호출 후 setInterval 반복, 코드 해제·언마운트 시 정리
+          <t>세션 코드가 있는 동안 1.5초 간격으로 GET /sessions/:code를 주기적으로 호출해 트랙 목록 갱신(실시간 아님)
+응답 트랙으로 레이어 목록과 트랙 수 표시를 교체
+진입 즉시 1회 호출 후 주기적으로 반복하고, 코드 해제·언마운트 시 정리
 - 폴링 실패(오프라인·프리로드 세션) 시 : 예외 무시하고 기존 화면 유지
-- 다른 참가자가 트랙 얹었을 때 : 다음 폴링에서 새 트랙 반영(반영 3초 이내 목표)</t>
+- 다른 참가자가 트랙 얹었을 때 : 다음 호출에서 새 트랙 반영(반영 3초 이내 목표)</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
@@ -2339,11 +2339,11 @@
       <c r="J37" s="13" t="inlineStr">
         <is>
           <t>모든 레이어와 현재 take를 합쳐 트랙별 녹음 악기·스타일로 동시 재생
-트랙마다 createVoice로 보이스 생성, 오디오 클럭 기준 scheduleEvents로 샘플정확 스케줄(레이어 싱크)
-가장 긴 트랙 길이+1.5초 후 자동 정지, 보이스 dispose
+트랙마다 보이스를 만들고, 오디오 클럭 기준으로 이벤트를 샘플 정확도로 예약 재생(레이어 싱크)
+가장 긴 트랙 길이+1.5초 후 자동 정지, 보이스 정리
 재생 시작 시 단일 take 재생·합주 재생 상호 정지
 - 합칠 트랙 없을 때 : 동작 중단
-- 재생 중 다시 누르면 : stopJam으로 즉시 정지(버튼 토글)
+- 재생 중 다시 누르면 : 즉시 정지(버튼 토글)
 - 라우트 이탈·언마운트 시 : 보이스 정리로 잔류음 방지</t>
         </is>
       </c>
@@ -2399,8 +2399,8 @@
 가져온 곡(서버 code) 위에 쌓은 경우 그 code를 출처(origin_code)로 강제 기록해 원작자 표시
 발행 후 나머지 레이어를 소유자 검증 키와 함께 순차 업로드
 - 곡 이름에 링크·이메일·전화번호 포함 시 : 서버 400, '연락처·링크는 넣을 수 없어요' 토스트
-- 같은 곡(첫 트랙 해시·트랙 수 동일) 재게시 시 : 서버 dedup, 기존 코드 멱등 반환, 추가 업로드 생략
-- 파생곡(출처 있음) 게시 시 : dedup 우회, '원작자 소스가 함께 표시돼요' 토스트
+- 같은 곡(첫 트랙 해시·트랙 수 동일) 재게시 시 : 서버 중복 제거, 기존 코드 멱등 반환, 추가 업로드 생략
+- 파생곡(출처 있음) 게시 시 : 중복 제거 우회, '원작자 소스가 함께 표시돼요' 토스트
 - 업로드 실패 시 : '올리기 실패 네트워크 확인' 토스트</t>
         </is>
       </c>
@@ -2473,17 +2473,17 @@
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>커뮤니티 진입 시 listCommunity(30)로 보드 목록 1회 조회(공개·미숨김 세션만, events 제외 메타만)
-조회 시 x-anon-key 헤더로 익명키 전송, 항목별 내 좋아요 여부(liked) 포함
+          <t>커뮤니티 진입 시 보드 목록을 30개 한도로 1회 조회(공개·미숨김 세션만, events 제외 메타만)
+조회 시 x-anon-key 헤더로 익명키 전송, 항목별 내 좋아요 여부 포함
 서버 기본 정렬은 created_at 내림차순, 동률은 code 내림차순
 각 카드에 이모지 아바타·음원명·작성자·트랙 수·재생 수·이어(파생) 수·출처 크레딧 표시
 메타 라벨은 '트랙 N개', '▶ 재생수', '이어 파생수'로 노출
-출처(originCode)가 있으면 '소스: ○○님의 「원곡명」 음원 사용' 크레딧 줄 표시
+출처 코드가 있으면 '소스: ○○님의 「원곡명」 음원 사용' 크레딧 줄 표시
 정렬 토글 제공: 최신순(서버 순서 그대로), 인기순(좋아요 수 내림차순 정렬, 동률은 안정 정렬로 최신 유지)
 페이지당 개수는 화면 높이로 동적 산출(floor((높이-240)/116), 3~12개로 제한), 리사이즈·회전 시 재계산
 페이지 2개 이상이면 이전·다음 페이저 노출, 리사이즈로 페이지 수 줄면 현재 페이지 자동 보정
 새로고침 버튼(↻)으로 목록 재조회, 조회 중에는 버튼 비활성
-- 로딩 중 : '불러오는 중...' 표시(items=null)
+- 로딩 중 : '불러오는 중...' 표시(아직 목록 없음)
 - 빈 목록 시 : '아직 음원이 없어요. 첫 곡의 주인공이 되어보세요.' 안내 + '스튜디오로' 버튼(콜드스타트 시드곡 2개로 빈 화면 방지)
 - 조회 실패 시 : '불러오지 못했어요.' + '다시 시도' 버튼</t>
         </is>
@@ -2537,8 +2537,8 @@
       <c r="J41" s="13" t="inlineStr">
         <is>
           <t>카드의 들어보기(▶) 탭 시 해당 음원을 미리듣기 재생
-트랙(events)은 보드 목록에 없으므로 getSession(code)로 지연 로드, 마운트 동안 캐시(재생 시 재요청 안 함)
-첫 로드 시 서버 재생 수(playCount) 1 증가
+트랙(events)은 보드 목록에 없으므로 세션 단건 조회로 지연 로드, 마운트 동안 캐시(재생 시 재요청 안 함)
+첫 로드 시 서버 재생 수 1 증가
 오디오 unlock 후 0ms부터 모든 트랙 동시 재생(트랙별 악기·스타일 적용)
 곡 중간부터 재생 시 시작 시점에 켜져 있던 코드·멜로디 노트를 즉시 attack해 무음 방지(sustain 보정)
 같은 카드 재탭 시 재생·일시정지 토글(위치 유지), 끝까지 재생되면 처음부터 재생
@@ -2599,12 +2599,12 @@
       <c r="J42" s="13" t="inlineStr">
         <is>
           <t>카드의 담기(＋) 탭으로 음원 다중 선택, 재탭 시 선택 해제, 선택 시 하단 가져오기 바 노출
-가져오기 탭 시 선택한 각 code를 getSession으로 확보(병렬)해 스튜디오로 적재
-단일 담기 : 해당 곡 위에 쌓기, 원본 code를 originCode로 보존(이후 합주 올리기의 출처로 강제)
+가져오기 탭 시 선택한 각 코드의 세션을 병렬로 확보해 스튜디오로 적재
+단일 담기 : 해당 곡 위에 쌓기, 원본 코드를 출처로 보존(이후 합주 올리기의 출처로 강제)
 다중 담기 : 선택 곡들의 트랙을 하나의 로컬 합본(code=LOCAL-import)으로 합쳐 적재, 출처 없음(재료 합본)
-올리기(＋ 올리기) 시트에서 내가 녹음한 곡 목록 표시, 곡 선택 후 publishSession으로 보드에 공개
-공개 시 닉네임을 작성자·소유자로, 익명키를 author_key로 전송, 첫 트랙 외 트랙은 addTrack으로 순차 적재
-중복방지 : 같은 익명키+첫 트랙 콘텐츠 해시+트랙 수가 이미 공개돼 있으면 새로 만들지 않고 기존 code 반환(deduped)
+올리기(＋ 올리기) 시트에서 내가 녹음한 곡 목록 표시, 곡 선택 후 보드에 공개
+공개 시 닉네임을 작성자·소유자로, 익명키를 작성자 키로 전송, 첫 트랙 외 트랙은 순차 적재
+중복방지 : 같은 익명키+첫 트랙 콘텐츠 해시+트랙 수가 이미 공개돼 있으면 새로 만들지 않고 기존 코드 반환(deduped)
 deduped인 경우 추가 트랙 적재를 건너뛰어 기존 세션 오염 방지
 - 공개 성공 시 : '보드에 올라갔어요' 토스트 후 목록 재조회
 - 중복 곡인 경우 : '같은 곡이 이미 보드에 있어요. 새로 올리지 않았어요' 토스트(새로 올리지 않음)
@@ -2663,13 +2663,13 @@
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>댓글(💬) 탭 시 패널 토글, 펼치면 getComments(code)로 댓글 목록 조회(미숨김만, 최신순)
-댓글 입력(placeholder '한마디 남기기', 최대 200자) 후 보내기 시 닉네임·익명키와 함께 addComment 전송, 성공 시 목록 갱신·첫 페이지 이동·카드 댓글 수 +1
+          <t>댓글(💬) 탭 시 패널 토글, 펼치면 해당 코드의 댓글 목록 조회(미숨김만, 최신순)
+댓글 입력(placeholder '한마디 남기기', 최대 200자) 후 보내기 시 닉네임·익명키와 함께 전송, 성공 시 목록 갱신·첫 페이지 이동·카드 댓글 수 +1
 댓글도 화면 높이 기준 동적 페이징(이전·다음), 펼칠 때 첫 페이지로 초기화
 각 댓글에 신고 버튼 제공, 신고는 조용히 접수(즉시 화면에서 제거하지 않음)
 신고 시 서버는 서로 다른 신고자(IP 기준) 1인 1회로 누적, 3명 이상 누적 시 해당 댓글 자동 숨김(소급 적용 없음)
 신고한 댓글은 이번 세션 동안 '신고됨'으로 표시·재신고 차단
-좋아요(하트) 탭 시 toggleLike로 토글, 익명키당 1회(켜짐·꺼짐), 낙관적 갱신 후 서버 응답(liked·count)으로 보정
+좋아요(하트) 탭 시 토글, 익명키당 1회(켜짐·꺼짐), 낙관적 갱신 후 서버 응답(좋아요 여부·수)으로 보정
 서버는 댓글·이름 텍스트에서 URL·이메일·전화번호 거부, 제어문자 제거·공백 정규화
 동일 익명키+동일 텍스트 60초 내 재전송은 멱등 처리(중복 무시)
 - 댓글 로딩 중 : '댓글 불러오는 중...' 표시
@@ -2808,7 +2808,7 @@
 선택지 24종 6열 그리드 표시(🎵 🎸 🎹 🥁 🎤 🎧 등)
 현재 선택 이모지는 파란 테두리·연파랑 배경으로 강조
 이모지 탭 시 localStorage harmony.emoji에 저장 후 화면 즉시 반영, 시트 닫힘
-- 배경(backdrop) 탭 시 : 선택 없이 시트 닫힘
+- 배경 영역 탭 시 : 선택 없이 시트 닫힘
 - 가입·로그인 절차 없음, 로컬 저장만 수행</t>
         </is>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="J47" s="13" t="inlineStr">
         <is>
           <t>정보 카드에 닉네임·버전 행 표시
-버전은 코드 상수 1.0.0 고정 표기
+버전은 코드에 고정된 상수 1.0.0으로 표기
 닉네임은 저장값 표시, 미저장 시 - 표시
 - 닉네임은 이 화면에서 변경 기능 없음(온보딩에서 입력)</t>
         </is>
@@ -2912,7 +2912,7 @@
         <is>
           <t>개발자 모드 카드 탭 시 토글 on/off 전환
 부제 안내: FPS · 네트워크 · 손 스켈레톤 표시
-상태는 localStorage harmony.devmode에 1/0으로 저장(상위 App에서 setDevMode 호출)
+상태는 localStorage harmony.devmode에 1/0으로 저장(상위 App으로 개발자 모드 상태를 올려 보냄)
 - on 전환 시 : 하단 2트랙 실증 패널 노출
 - off 전환 시 : 2트랙 실증 패널 숨김
 - localStorage 접근 실패 시 : 기본 false(off)</t>
@@ -2964,11 +2964,11 @@
         <is>
           <t>개발자 모드 on일 때만 노출되는 실증 패널
 실행 환경 표시: web은 web (브라우저/AWS), 그 외 런타임 환경 문자열 표시
-식별키 표시: getUserKey 비동기 조회값, 16자 초과 시 앞 16자 + ... 로 축약
+식별키 표시: 실행 환경에 맞는 익명 식별키를 비동기로 조회한 값, 16자 초과 시 앞 16자 + ... 로 축약
 - 토스 환경 성공 시 : toss_ 접두 hash
 - 일반 브라우저·미지원 시 : anon_ 접두 익명키
 - 조회 전 초기값 : ... 표시
-TDS 렌더 행: 토스 환경이면 TdsBadge 동적 로드(로딩 중 로딩... 표시), 웹이면 미적용 (web) 표시</t>
+TDS 렌더 행: 토스 환경이면 TDS 배지 컴포넌트를 지연 로드(로딩 중 로딩... 표시), 웹이면 미적용 (web) 표시</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
@@ -3022,9 +3022,9 @@
           <t>법적 고지 섹션에 이용약관·개인정보 처리방침 행 표시
 각 행 탭 시 해당 문서를 스크롤 가능한 바텀시트 모달로 표시
 모달에 제목·갱신일·도입문·섹션별 제목·문단(불릿) 렌더
-닫기 버튼 또는 배경(backdrop) 탭 시 모달 닫힘
+닫기 버튼 또는 배경 영역 탭 시 모달 닫힘
 안내 문구: 고객센터는 토스 공통 메뉴 이용, 토스 익명 식별만 사용·별도 개인정보 미수집 명시
-- 문서 본문 내용은 lib/legal.ts TERMS·PRIVACY 상수에서 로드</t>
+- 문서 본문 내용은 약관·개인정보 처리방침 텍스트 상수에서 로드</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>하단 홈으로 버튼 탭 시 go('home') 호출로 홈 라우트 이동
+          <t>하단 홈으로 버튼 탭 시 홈 라우트로 이동
 - 별도 확인 절차 없이 즉시 이동</t>
         </is>
       </c>
@@ -3125,9 +3125,9 @@
         <is>
           <t>제스처 효과음(탬버린·박수·헤드뱅잉) on/off 상태를 localStorage harmony.fxon에 저장
 저장값이 0이 아니면 on으로 해석, 기본값 on
-setFxOn(true) 시 1 저장, setFxOn(false) 시 0 저장
+on으로 설정 시 1 저장, off로 설정 시 0 저장
 - localStorage 접근 실패 시 : 조회는 기본 true(on), 저장은 무시
-- 비고: 토글 상태·읽기/쓰기 함수만 lib/settings.ts에 정의, Settings.tsx 화면에는 토글 UI 미배치</t>
+- 비고: 토글 상태·읽기/쓰기 로직만 설정 모듈에 정의, 설정 화면에는 토글 UI 미배치</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
